--- a/artfynd/A 13974-2022 artfynd.xlsx
+++ b/artfynd/A 13974-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13974-2022 artfynd.xlsx
+++ b/artfynd/A 13974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89595746</v>
+        <v>103282905</v>
       </c>
       <c r="B2" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råttenhållan, Hjd</t>
+          <t>Granåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430836.9051386286</v>
+        <v>430789</v>
       </c>
       <c r="R2" t="n">
-        <v>6841778.967159319</v>
+        <v>6841570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89595749</v>
+        <v>103282919</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råttenhållan, Hjd</t>
+          <t>Granåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430831.2048945497</v>
+        <v>430779</v>
       </c>
       <c r="R3" t="n">
-        <v>6841779.081748535</v>
+        <v>6841538</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,31 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>89595775</v>
       </c>
       <c r="B4" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430799.157426733</v>
+        <v>430799</v>
       </c>
       <c r="R4" t="n">
-        <v>6841863.23606071</v>
+        <v>6841863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +937,9 @@
           <t>2020-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89595743</v>
+        <v>103282898</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,37 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råttenhållan, Hjd</t>
+          <t>Granåsen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430838.8433560365</v>
+        <v>430766</v>
       </c>
       <c r="R5" t="n">
-        <v>6841780.826172595</v>
+        <v>6841804</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,31 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89595764</v>
+        <v>103282902</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,37 +1078,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råttenhållan, Hjd</t>
+          <t>Granåsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430834.1980363883</v>
+        <v>430756</v>
       </c>
       <c r="R6" t="n">
-        <v>6841786.138975675</v>
+        <v>6841757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,53 +1152,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103282914</v>
+        <v>103282910</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>430777.1957607341</v>
+        <v>430712</v>
       </c>
       <c r="R7" t="n">
-        <v>6841999.851623094</v>
+        <v>6841617</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,19 +1232,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,15 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103282909</v>
+        <v>103282885</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>430719.6291958042</v>
+        <v>430760</v>
       </c>
       <c r="R8" t="n">
-        <v>6841571.593845015</v>
+        <v>6841550</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,19 +1329,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103282883</v>
+        <v>103282887</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430811.6893247535</v>
+        <v>430748</v>
       </c>
       <c r="R9" t="n">
-        <v>6841635.699528469</v>
+        <v>6841456</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,19 +1426,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,37 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103282885</v>
+        <v>103282930</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>430760.0634545675</v>
+        <v>430748</v>
       </c>
       <c r="R10" t="n">
-        <v>6841549.900906755</v>
+        <v>6841437</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,19 +1523,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,15 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103282896</v>
+        <v>103282891</v>
       </c>
       <c r="B11" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430763.0288410881</v>
+        <v>430710</v>
       </c>
       <c r="R11" t="n">
-        <v>6841768.116126086</v>
+        <v>6842116</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,19 +1620,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,15 +1649,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103282888</v>
+        <v>103282921</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,21 +1660,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>430731.3312385331</v>
+        <v>430797</v>
       </c>
       <c r="R12" t="n">
-        <v>6841444.658326107</v>
+        <v>6841530</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,19 +1717,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,37 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103282884</v>
+        <v>103282883</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>430830.6270468519</v>
+        <v>430812</v>
       </c>
       <c r="R13" t="n">
-        <v>6842057.609939502</v>
+        <v>6841635</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,19 +1814,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,19 +1843,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103282925</v>
+        <v>103282892</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2080,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>430692.9260393198</v>
+        <v>430801</v>
       </c>
       <c r="R14" t="n">
-        <v>6842109.724324058</v>
+        <v>6842047</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,19 +1911,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,15 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103282887</v>
+        <v>103282899</v>
       </c>
       <c r="B15" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,21 +1951,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2192,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430748.1876795685</v>
+        <v>430715</v>
       </c>
       <c r="R15" t="n">
-        <v>6841455.707996088</v>
+        <v>6842110</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,19 +2008,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,15 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103282903</v>
+        <v>103282920</v>
       </c>
       <c r="B16" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2048,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430829.3819555966</v>
+        <v>430710</v>
       </c>
       <c r="R16" t="n">
-        <v>6841664.763520597</v>
+        <v>6841615</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,19 +2105,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,37 +2134,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103282894</v>
+        <v>103282925</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>430713.8440341965</v>
+        <v>430693</v>
       </c>
       <c r="R17" t="n">
-        <v>6842110.251871306</v>
+        <v>6842110</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,19 +2202,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,15 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103282892</v>
+        <v>103282893</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>430800.9587652341</v>
+        <v>430731</v>
       </c>
       <c r="R18" t="n">
-        <v>6842047.294071376</v>
+        <v>6841444</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2561,19 +2299,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,37 +2328,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103282910</v>
+        <v>103282904</v>
       </c>
       <c r="B19" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>430711.995247195</v>
+        <v>430815</v>
       </c>
       <c r="R19" t="n">
-        <v>6841617.301458092</v>
+        <v>6841716</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2673,19 +2396,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,15 +2425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103282899</v>
+        <v>103282894</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,21 +2436,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2752,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>430714.7939836083</v>
+        <v>430714</v>
       </c>
       <c r="R20" t="n">
-        <v>6842110.232739505</v>
+        <v>6842110</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2785,19 +2493,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,15 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103282919</v>
+        <v>103282886</v>
       </c>
       <c r="B21" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2840,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2864,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>430779.3115806996</v>
+        <v>430728</v>
       </c>
       <c r="R21" t="n">
-        <v>6841538.12501215</v>
+        <v>6841446</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,19 +2590,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,15 +2619,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103282911</v>
+        <v>103282896</v>
       </c>
       <c r="B22" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,21 +2630,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2976,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430772.0949360459</v>
+        <v>430763</v>
       </c>
       <c r="R22" t="n">
-        <v>6842006.122282105</v>
+        <v>6841768</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,19 +2687,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,15 +2716,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103282923</v>
+        <v>103282909</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,21 +2727,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430849.7104642129</v>
+        <v>430720</v>
       </c>
       <c r="R23" t="n">
-        <v>6842037.773583523</v>
+        <v>6841571</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,19 +2784,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,15 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103282917</v>
+        <v>103282913</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3200,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430745.1422487856</v>
+        <v>430731</v>
       </c>
       <c r="R24" t="n">
-        <v>6842083.526884375</v>
+        <v>6841444</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,19 +2881,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,15 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103282905</v>
+        <v>103282914</v>
       </c>
       <c r="B25" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3288,21 +2921,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3312,10 +2945,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430788.5113209559</v>
+        <v>430777</v>
       </c>
       <c r="R25" t="n">
-        <v>6841570.207648375</v>
+        <v>6842000</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,19 +2978,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,15 +3007,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103282886</v>
+        <v>103282917</v>
       </c>
       <c r="B26" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3424,10 +3042,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430728.0439684778</v>
+        <v>430745</v>
       </c>
       <c r="R26" t="n">
-        <v>6841446.622660487</v>
+        <v>6842083</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,19 +3075,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3496,15 +3104,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103282891</v>
+        <v>103282927</v>
       </c>
       <c r="B27" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,21 +3115,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3536,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430710.1588608419</v>
+        <v>430766</v>
       </c>
       <c r="R27" t="n">
-        <v>6842116.019475411</v>
+        <v>6841803</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,19 +3172,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3608,15 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103282913</v>
+        <v>103282915</v>
       </c>
       <c r="B28" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,34 +3212,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granåsen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430731.3312385331</v>
+        <v>430695</v>
       </c>
       <c r="R28" t="n">
-        <v>6841444.658326107</v>
+        <v>6841608</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,19 +3277,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,15 +3306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103282902</v>
+        <v>103282888</v>
       </c>
       <c r="B29" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,21 +3317,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3760,10 +3341,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430756.6244690687</v>
+        <v>430731</v>
       </c>
       <c r="R29" t="n">
-        <v>6841756.857093066</v>
+        <v>6841444</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3793,19 +3374,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3832,15 +3403,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103282920</v>
+        <v>103282911</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3848,21 +3414,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3872,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430710.0568696542</v>
+        <v>430772</v>
       </c>
       <c r="R30" t="n">
-        <v>6841615.442424037</v>
+        <v>6842006</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3905,19 +3471,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3944,15 +3500,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103282898</v>
+        <v>103282923</v>
       </c>
       <c r="B31" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3960,21 +3511,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3984,10 +3535,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430765.6542838538</v>
+        <v>430850</v>
       </c>
       <c r="R31" t="n">
-        <v>6841804.124774601</v>
+        <v>6842038</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4017,19 +3568,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,37 +3597,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103282893</v>
+        <v>103282903</v>
       </c>
       <c r="B32" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4096,10 +3632,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430731.3312385331</v>
+        <v>430830</v>
       </c>
       <c r="R32" t="n">
-        <v>6841444.658326107</v>
+        <v>6841665</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4129,19 +3665,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4168,37 +3694,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103282927</v>
+        <v>103282916</v>
       </c>
       <c r="B33" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4208,10 +3729,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430765.6256515157</v>
+        <v>430862</v>
       </c>
       <c r="R33" t="n">
-        <v>6841802.701878442</v>
+        <v>6841744</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4241,19 +3762,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4280,37 +3791,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103282930</v>
+        <v>103282884</v>
       </c>
       <c r="B34" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +3826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430747.3307617262</v>
+        <v>430831</v>
       </c>
       <c r="R34" t="n">
-        <v>6841436.74364381</v>
+        <v>6842058</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4353,19 +3859,9 @@
           <t>2022-08-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,15 +3888,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103282915</v>
+        <v>89595749</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4408,45 +3899,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granåsen, Hjd</t>
+          <t>Råttenhållan, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430695.1776777734</v>
+        <v>430831</v>
       </c>
       <c r="R35" t="n">
-        <v>6841608.149802858</v>
+        <v>6841779</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4470,22 +3953,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4500,15 +3973,323 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>89595764</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Råttenhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>430834</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6841786</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>89595746</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Råttenhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>430837</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6841779</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>89595743</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Råttenhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>430839</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6841781</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13974-2022 artfynd.xlsx
+++ b/artfynd/A 13974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282919</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282898</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282923</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282903</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282910</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282930</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282891</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282921</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282883</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282892</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282899</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282916</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282920</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282925</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282893</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282884</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595749</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282894</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595764</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282886</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282896</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282909</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3497,6 +3642,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282913</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3594,6 +3744,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282914</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3691,6 +3846,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282917</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282927</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3890,6 +4055,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595746</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,6 +4165,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282915</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4092,6 +4267,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282888</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4189,6 +4369,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103282911</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4290,8 +4475,52 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>